--- a/content/01_기획/files/2026-07-13_A2팀_기능명세서_초안_v0.4.xlsx
+++ b/content/01_기획/files/2026-07-13_A2팀_기능명세서_초안_v0.4.xlsx
@@ -1176,7 +1176,6 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C20:H20"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="C19:H19"/>
@@ -1190,6 +1189,7 @@
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C20:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>영상 입력 검증·한도</t>
+          <t>영상 입력 검증</t>
         </is>
       </c>
       <c r="D35" s="30" t="inlineStr">
@@ -3957,17 +3957,17 @@
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
-          <t>이미지·프롬프트·옵션·한도</t>
+          <t>이미지·프롬프트·옵션</t>
         </is>
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>입력 검증. 한도 도달 시 카운터 없이 요청 차단</t>
+          <t>입력 검증. 잘못된 요청 차단</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
-          <t>오류·한도 안내</t>
+          <t>오류 안내</t>
         </is>
       </c>
       <c r="H35" s="30" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="I35" s="30" t="inlineStr">
         <is>
-          <t>validation·limit 응답 형식 확인</t>
+          <t>validation 응답 형식 확인</t>
         </is>
       </c>
       <c r="J35" s="30" t="inlineStr">
         <is>
-          <t>잘못된 입력과 한도 초과 요청이 생성 API로 전달되지 않는다</t>
+          <t>잘못된 입력이 생성 API로 전달되지 않는다</t>
         </is>
       </c>
       <c r="K35" s="30" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="L35" s="30" t="inlineStr">
         <is>
-          <t>IA-083~084</t>
+          <t>IA-083</t>
         </is>
       </c>
       <c r="M35" s="36" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Q35" s="30" t="inlineStr">
         <is>
-          <t>노션에 항목 없음(한도) — 일일 한도 구현 확인 ❓</t>
+          <t>노션에 항목 없음(검증) — 범위 확인 ❓</t>
         </is>
       </c>
     </row>
@@ -6328,17 +6328,17 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>IA-084</t>
+          <t>IA-084(삭제 필요)</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제외(07-15)</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>한도값 BE 확인</t>
+          <t>일일 한도·크레딧 미적용 확정으로 범위 제외</t>
         </is>
       </c>
     </row>

--- a/content/01_기획/files/2026-07-13_A2팀_기능명세서_초안_v0.4.xlsx
+++ b/content/01_기획/files/2026-07-13_A2팀_기능명세서_초안_v0.4.xlsx
@@ -1175,21 +1175,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C19:H19"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C19:H19"/>
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="C18:H18"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C20:H20"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C20:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>중복 이메일·미인증·미동의 시 완료 차단</t>
+          <t>중복 이메일(Google 가입 이메일 포함)·미인증·미동의 시 완료 차단</t>
         </is>
       </c>
       <c r="I6" s="30" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
-          <t>OAuth 취소·실패 시 로그인 화면 유지와 오류 표시</t>
+          <t>OAuth 취소·실패 시 로그인 화면 유지와 오류 표시 · 일반 가입 이메일은 Google 가입 차단</t>
         </is>
       </c>
       <c r="I7" s="30" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>Google 계정 연결 관리</t>
+          <t>가입 방식 표시</t>
         </is>
       </c>
       <c r="D45" s="30" t="inlineStr">
@@ -4827,32 +4827,32 @@
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>연결 상태·해제</t>
+          <t>가입 방식 확인</t>
         </is>
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>가입 방식에 따라 화면 분기 후 연결 관리</t>
+          <t>가입 방식에 따라 화면 분기, 가입 방식(일반/Google) 표시. 연결 추가·해제 없음</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>연결 계정 상태</t>
+          <t>가입 방식 표시</t>
         </is>
       </c>
       <c r="H45" s="30" t="inlineStr">
         <is>
-          <t>유일 로그인 수단 해제 정책 확인</t>
+          <t>가입 방식 배타로 유일 수단 해제 정책 확인 항목 해소</t>
         </is>
       </c>
       <c r="I45" s="30" t="inlineStr">
         <is>
-          <t>Google OAuth·계정 연결 API 미정</t>
+          <t>User 가입 방식 필드 확인</t>
         </is>
       </c>
       <c r="J45" s="30" t="inlineStr">
         <is>
-          <t>Google 사용자에게만 연결 상태와 가능한 액션이 보인다</t>
+          <t>가입 방식이 정확히 표시되고 연결·해제 액션이 노출되지 않는다</t>
         </is>
       </c>
       <c r="K45" s="30" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="Q45" s="30" t="inlineStr">
         <is>
-          <t>연결 관리 착수 여부 확인 ❓ (Google 로그인 자체는 AUTH-003)</t>
+          <t>이메일-가입 방식 배타 구현 완료 (로그인 자체는 AUTH-003)</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>Google 해제 정책</t>
+          <t>이메일-가입 방식 배타(07-15) — 연결·해제 없음</t>
         </is>
       </c>
     </row>

--- a/content/01_기획/files/2026-07-13_A2팀_기능명세서_초안_v0.4.xlsx
+++ b/content/01_기획/files/2026-07-13_A2팀_기능명세서_초안_v0.4.xlsx
@@ -1175,21 +1175,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C16:H16"/>
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C20:H20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>중복 이메일(Google 가입 이메일 포함)·미인증·미동의 시 완료 차단</t>
+          <t>중복 이메일·미인증·미동의 시 완료 차단</t>
         </is>
       </c>
       <c r="I6" s="30" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
-          <t>OAuth 취소·실패 시 로그인 화면 유지와 오류 표시 · 일반 가입 이메일은 Google 가입 차단</t>
+          <t>OAuth 취소·실패 시 로그인 화면 유지와 오류 표시</t>
         </is>
       </c>
       <c r="I7" s="30" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>가입 방식 표시</t>
+          <t>Google 계정 연결 관리</t>
         </is>
       </c>
       <c r="D45" s="30" t="inlineStr">
@@ -4827,32 +4827,32 @@
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>가입 방식 확인</t>
+          <t>연결 상태·해제</t>
         </is>
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>가입 방식에 따라 화면 분기, 가입 방식(일반/Google) 표시. 연결 추가·해제 없음</t>
+          <t>가입 방식에 따라 화면 분기 후 연결 관리</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>가입 방식 표시</t>
+          <t>연결 계정 상태</t>
         </is>
       </c>
       <c r="H45" s="30" t="inlineStr">
         <is>
-          <t>가입 방식 배타로 유일 수단 해제 정책 확인 항목 해소</t>
+          <t>유일 로그인 수단 해제 정책 확인</t>
         </is>
       </c>
       <c r="I45" s="30" t="inlineStr">
         <is>
-          <t>User 가입 방식 필드 확인</t>
+          <t>Google OAuth·계정 연결 API 미정</t>
         </is>
       </c>
       <c r="J45" s="30" t="inlineStr">
         <is>
-          <t>가입 방식이 정확히 표시되고 연결·해제 액션이 노출되지 않는다</t>
+          <t>Google 사용자에게만 연결 상태와 가능한 액션이 보인다</t>
         </is>
       </c>
       <c r="K45" s="30" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="Q45" s="30" t="inlineStr">
         <is>
-          <t>이메일-가입 방식 배타 구현 완료 (로그인 자체는 AUTH-003)</t>
+          <t>연결 관리 착수 여부 확인 ❓ (Google 로그인 자체는 AUTH-003)</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>이메일-가입 방식 배타(07-15) — 연결·해제 없음</t>
+          <t>Google 해제 정책</t>
         </is>
       </c>
     </row>
